--- a/Desafio 2 - Projeto - 11062025/Cronograma_Projeto_Documentos_Fiscais_Formatado.xlsx
+++ b/Desafio 2 - Projeto - 11062025/Cronograma_Projeto_Documentos_Fiscais_Formatado.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 2 - Projeto - 11062025\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C472736E-0D9A-4BED-847E-017E1830F2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OOdz4x58aIAhNqlZxZo+LxbmvLYL+6mfX/ydHE3rUv4="/>
@@ -41,35 +50,35 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">Levantamento de Requisitos                                                                                                      </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> - Análise detalhada de tipos de documentos fiscais brasileiros</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">   </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">                                                                                                             - Definição de campos obrigatórios para extração
 - Estudo de regulamentações fiscais aplicáveis
@@ -88,18 +97,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">Desenvolvimento OCR + NLP - Agente 2           </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        - Implementação do motor de OCR otimizado
 - Desenvolvimento de algoritmos de NLP para extração de campos
@@ -118,18 +127,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">Testes Iniciais      </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve">                                                                                                                            - Elaboração de Plano de Testes                                                                                                                                                                                                                                                       - Validação com conjunto de documentos de teste
 - Ajustes de precisão e correção de bugs
@@ -148,18 +157,18 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t xml:space="preserve"> Atividades Finais                                                                                                                              </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
       <t>- Planejamento de melhorias                                                                                                                                                                                                                                                   
 - Apresentação de métricas de precisão alcançadas                                                                                                                    - Demonstração do MVP funcional</t>
@@ -181,165 +190,167 @@
     <t>Fase 5</t>
   </si>
   <si>
+    <t>18/07 à 31/07</t>
+  </si>
+  <si>
+    <t>14 dias</t>
+  </si>
+  <si>
+    <t>Fase 6</t>
+  </si>
+  <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Atividades Finais       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                                                 - Demonstração do sistema completo
+- Casos reais e ROI
+- Roadmap futuro</t>
+    </r>
+  </si>
+  <si>
+    <t>01/08 à 14/08</t>
+  </si>
+  <si>
+    <t>Desafio 5 – Terceira Apresentação</t>
+  </si>
+  <si>
+    <t>15/08 à 04/09</t>
+  </si>
+  <si>
+    <t>Fase 7</t>
+  </si>
+  <si>
+    <t>Validação e Ajuste</t>
+  </si>
+  <si>
+    <t>15/08 à 23/08</t>
+  </si>
+  <si>
+    <t>- Testes com usuários finais
+- Correções e otimizações finais                                                                                                                                                                 - Preparação da documentação completa                                                                                 - Validação de compliance</t>
+  </si>
+  <si>
+    <t>Fase 8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b/>
+        <sz val="11"/>
         <color theme="1"/>
-        <sz val="11.0"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Apresentação final intermediária</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+- Entrega de código-fonte e documentação                                                                                                            - Demonstração de impacto e resultados                                                                                                                    - Plano de continuidade e manutenção</t>
+    </r>
+  </si>
+  <si>
+    <t>24/08 à 04/09</t>
+  </si>
+  <si>
+    <t>12 dias</t>
+  </si>
+  <si>
+    <t>Desafio 6 – Apresentação Final (Parte 1)</t>
+  </si>
+  <si>
+    <t>05/09 à 25/09</t>
+  </si>
+  <si>
+    <t>Fase 9</t>
+  </si>
+  <si>
+    <t>- Entrega de código-fonte e documentação</t>
+  </si>
+  <si>
+    <t>21 dias</t>
+  </si>
+  <si>
+    <t>Desafio 6 – Apresentação Final (Parte 2)</t>
+  </si>
+  <si>
+    <t>26/09 à 02/10</t>
+  </si>
+  <si>
+    <t>Fase 10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>Interface - Agente 1 + Frontend</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
       </rPr>
-      <t xml:space="preserve">                                                                                                                                                                                                                                  - Desenvolvimento de APIs para download de arquivos
-- Criação de interface web
+      <t xml:space="preserve">                                                                                                                                                                                                                                  - Criação de interface web
 - Implementação de funcionalidades avançadas
 - Testes de download de dados com sites reais</t>
     </r>
-  </si>
-  <si>
-    <t>18/07 à 31/07</t>
-  </si>
-  <si>
-    <t>14 dias</t>
-  </si>
-  <si>
-    <t>Fase 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">Atividades Finais       </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                                                 - Demonstração do sistema completo
-- Casos reais e ROI
-- Roadmap futuro</t>
-    </r>
-  </si>
-  <si>
-    <t>01/08 à 14/08</t>
-  </si>
-  <si>
-    <t>Desafio 5 – Terceira Apresentação</t>
-  </si>
-  <si>
-    <t>15/08 à 04/09</t>
-  </si>
-  <si>
-    <t>Fase 7</t>
-  </si>
-  <si>
-    <t>Validação e Ajuste</t>
-  </si>
-  <si>
-    <t>15/08 à 23/08</t>
-  </si>
-  <si>
-    <t>- Testes com usuários finais
-- Correções e otimizações finais                                                                                                                                                                 - Preparação da documentação completa                                                                                 - Validação de compliance</t>
-  </si>
-  <si>
-    <t>Fase 8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Apresentação final intermediária</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">
-- Entrega de código-fonte e documentação                                                                                                            - Demonstração de impacto e resultados                                                                                                                    - Plano de continuidade e manutenção</t>
-    </r>
-  </si>
-  <si>
-    <t>24/08 à 04/09</t>
-  </si>
-  <si>
-    <t>12 dias</t>
-  </si>
-  <si>
-    <t>Desafio 6 – Apresentação Final (Parte 1)</t>
-  </si>
-  <si>
-    <t>05/09 à 25/09</t>
-  </si>
-  <si>
-    <t>Fase 9</t>
-  </si>
-  <si>
-    <t>- Entrega de código-fonte e documentação</t>
-  </si>
-  <si>
-    <t>21 dias</t>
-  </si>
-  <si>
-    <t>Desafio 6 – Apresentação Final (Parte 2)</t>
-  </si>
-  <si>
-    <t>26/09 à 02/10</t>
-  </si>
-  <si>
-    <t>Fase 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -349,7 +360,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -383,7 +394,13 @@
     </fill>
   </fills>
   <borders count="8">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -397,19 +414,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -419,6 +440,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -431,6 +453,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -439,9 +462,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -453,6 +478,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -461,91 +488,98 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -735,24 +769,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.0"/>
-    <col customWidth="1" min="2" max="2" width="67.29"/>
-    <col customWidth="1" min="3" max="3" width="16.71"/>
-    <col customWidth="1" min="4" max="4" width="14.0"/>
-    <col customWidth="1" min="5" max="26" width="8.71"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="67.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,216 +800,216 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="18.0" customHeight="1">
+    <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="20"/>
     </row>
-    <row r="3" ht="87.0" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:4" ht="87" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="82.5" customHeight="1">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:4" ht="82.5" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="79.5" customHeight="1">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" ht="79.5" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="77.25" customHeight="1">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:4" ht="77.25" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:4">
+      <c r="A7" s="8"/>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="20"/>
     </row>
-    <row r="8" ht="90.75" customHeight="1">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" ht="90.75" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="79.5" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="B9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="9" ht="79.5" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="20.25" customHeight="1">
+    <row r="10" spans="1:4" ht="20.25" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="B11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="11" ht="20.25" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="14" t="s">
+    <row r="12" spans="1:4" ht="67.5" customHeight="1">
+      <c r="A12" s="22"/>
+      <c r="B12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>17</v>
-      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
     </row>
-    <row r="12" ht="67.5" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+    <row r="13" spans="1:4" ht="80.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="B13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="13" ht="80.25" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="14" t="s">
+    <row r="14" spans="1:4" ht="21.75" customHeight="1">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
         <v>40</v>
       </c>
+      <c r="C14" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="20"/>
     </row>
-    <row r="14" ht="21.75" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18" t="s">
+    <row r="15" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="5"/>
+      <c r="D15" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="15" ht="34.5" customHeight="1">
-      <c r="A15" s="6" t="s">
+    <row r="16" spans="1:4" ht="22.5" customHeight="1">
+      <c r="A16" s="17"/>
+      <c r="B16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>45</v>
+      <c r="C17" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" ht="32.25" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1946,18 +1980,16 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>